--- a/public/downloads/monthly-budget-planner.xlsx
+++ b/public/downloads/monthly-budget-planner.xlsx
@@ -61,7 +61,7 @@
     <t>Add the name on the Categories sheet, then copy the last row of the Budget table down. The SUMIFS formula adjusts itself.</t>
   </si>
   <si>
-    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modelling convention.</t>
+    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention.</t>
   </si>
   <si>
     <t>Categories</t>
@@ -198,8 +198,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -831,7 +831,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -946,7 +946,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -2493,7 +2493,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -2808,7 +2808,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/public/downloads/monthly-budget-planner.xlsx
+++ b/public/downloads/monthly-budget-planner.xlsx
@@ -718,33 +718,28 @@
     <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -754,7 +749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -764,22 +759,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -789,12 +784,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
@@ -804,7 +799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
@@ -814,7 +809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
